--- a/docs/detail-design/07_ChiTietDon.xlsx
+++ b/docs/detail-design/07_ChiTietDon.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="343">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · CHI TIẾT ĐƠN</t>
   </si>
@@ -139,6 +139,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Form Trả phòng / thu tiền: hai ô trên một hàng tự xuống dòng khi hẹp, ô ngày giờ không còn tràn khung.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Đơn Đã đặt (khách tự check-in, Quản lý xem)</t>
   </si>
   <si>
@@ -563,6 +569,9 @@
   </si>
   <si>
     <t>Giờ nhận thực tế đã ghi, chưa có thì giờ hẹn nhận</t>
+  </si>
+  <si>
+    <t>Hai ô ngày giờ (và hai ô Số tiền / Hình thức ở form thu tiền) nằm cùng hàng khi khung đủ rộng (mỗi ô ≥ 210px), hẹp thì xuống dòng — không tràn khung chi tiết.</t>
   </si>
   <si>
     <t>Giờ trả thực tế</t>
@@ -1274,7 +1283,7 @@
       <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4114800" cy="11630025"/>
+    <xdr:ext cx="4114800" cy="12363450"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -1310,10 +1319,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>178</xdr:row>
+      <xdr:row>181</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4114800" cy="13134975"/>
+    <xdr:ext cx="4114800" cy="13868400"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -1349,7 +1358,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>250</xdr:row>
+      <xdr:row>257</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4114800" cy="13382625"/>
@@ -1388,7 +1397,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>324</xdr:row>
+      <xdr:row>331</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4114800" cy="8591550"/>
@@ -1427,7 +1436,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>373</xdr:row>
+      <xdr:row>380</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4114800" cy="10287000"/>
@@ -1466,7 +1475,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>431</xdr:row>
+      <xdr:row>438</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4114800" cy="10010775"/>
@@ -1873,7 +1882,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2604,8 +2613,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -2645,6 +2696,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -2655,7 +2710,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG431"/>
+  <dimension ref="B1:AG438"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2664,7 +2719,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2700,7 +2755,7 @@
     </row>
     <row r="56" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -2736,7 +2791,7 @@
     </row>
     <row r="112" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B112" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -2770,270 +2825,270 @@
       <c r="AF112" s="4"/>
       <c r="AG112" s="4"/>
     </row>
-    <row r="177" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B177" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="4"/>
-      <c r="L177" s="4"/>
-      <c r="M177" s="4"/>
-      <c r="N177" s="4"/>
-      <c r="O177" s="4"/>
-      <c r="P177" s="4"/>
-      <c r="Q177" s="4"/>
-      <c r="R177" s="4"/>
-      <c r="S177" s="4"/>
-      <c r="T177" s="4"/>
-      <c r="U177" s="4"/>
-      <c r="V177" s="4"/>
-      <c r="W177" s="4"/>
-      <c r="X177" s="4"/>
-      <c r="Y177" s="4"/>
-      <c r="Z177" s="4"/>
-      <c r="AA177" s="4"/>
-      <c r="AB177" s="4"/>
-      <c r="AC177" s="4"/>
-      <c r="AD177" s="4"/>
-      <c r="AE177" s="4"/>
-      <c r="AF177" s="4"/>
-      <c r="AG177" s="4"/>
-    </row>
-    <row r="178" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B178" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
-      <c r="M178" s="6"/>
-      <c r="N178" s="6"/>
-      <c r="O178" s="6"/>
-      <c r="P178" s="6"/>
-      <c r="Q178" s="6"/>
-      <c r="R178" s="6"/>
-      <c r="S178" s="6"/>
-      <c r="T178" s="6"/>
-      <c r="U178" s="6"/>
-      <c r="V178" s="6"/>
-      <c r="W178" s="6"/>
-      <c r="X178" s="6"/>
-      <c r="Y178" s="6"/>
-      <c r="Z178" s="6"/>
-      <c r="AA178" s="6"/>
-      <c r="AB178" s="6"/>
-      <c r="AC178" s="6"/>
-      <c r="AD178" s="6"/>
-      <c r="AE178" s="6"/>
-      <c r="AF178" s="6"/>
-      <c r="AG178" s="6"/>
-    </row>
-    <row r="250" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B250" s="4" t="s">
+    <row r="180" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B180" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
-      <c r="I250" s="4"/>
-      <c r="J250" s="4"/>
-      <c r="K250" s="4"/>
-      <c r="L250" s="4"/>
-      <c r="M250" s="4"/>
-      <c r="N250" s="4"/>
-      <c r="O250" s="4"/>
-      <c r="P250" s="4"/>
-      <c r="Q250" s="4"/>
-      <c r="R250" s="4"/>
-      <c r="S250" s="4"/>
-      <c r="T250" s="4"/>
-      <c r="U250" s="4"/>
-      <c r="V250" s="4"/>
-      <c r="W250" s="4"/>
-      <c r="X250" s="4"/>
-      <c r="Y250" s="4"/>
-      <c r="Z250" s="4"/>
-      <c r="AA250" s="4"/>
-      <c r="AB250" s="4"/>
-      <c r="AC250" s="4"/>
-      <c r="AD250" s="4"/>
-      <c r="AE250" s="4"/>
-      <c r="AF250" s="4"/>
-      <c r="AG250" s="4"/>
-    </row>
-    <row r="324" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B324" s="4" t="s">
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
+      <c r="L180" s="4"/>
+      <c r="M180" s="4"/>
+      <c r="N180" s="4"/>
+      <c r="O180" s="4"/>
+      <c r="P180" s="4"/>
+      <c r="Q180" s="4"/>
+      <c r="R180" s="4"/>
+      <c r="S180" s="4"/>
+      <c r="T180" s="4"/>
+      <c r="U180" s="4"/>
+      <c r="V180" s="4"/>
+      <c r="W180" s="4"/>
+      <c r="X180" s="4"/>
+      <c r="Y180" s="4"/>
+      <c r="Z180" s="4"/>
+      <c r="AA180" s="4"/>
+      <c r="AB180" s="4"/>
+      <c r="AC180" s="4"/>
+      <c r="AD180" s="4"/>
+      <c r="AE180" s="4"/>
+      <c r="AF180" s="4"/>
+      <c r="AG180" s="4"/>
+    </row>
+    <row r="181" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B181" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C324" s="4"/>
-      <c r="D324" s="4"/>
-      <c r="E324" s="4"/>
-      <c r="F324" s="4"/>
-      <c r="G324" s="4"/>
-      <c r="H324" s="4"/>
-      <c r="I324" s="4"/>
-      <c r="J324" s="4"/>
-      <c r="K324" s="4"/>
-      <c r="L324" s="4"/>
-      <c r="M324" s="4"/>
-      <c r="N324" s="4"/>
-      <c r="O324" s="4"/>
-      <c r="P324" s="4"/>
-      <c r="Q324" s="4"/>
-      <c r="R324" s="4"/>
-      <c r="S324" s="4"/>
-      <c r="T324" s="4"/>
-      <c r="U324" s="4"/>
-      <c r="V324" s="4"/>
-      <c r="W324" s="4"/>
-      <c r="X324" s="4"/>
-      <c r="Y324" s="4"/>
-      <c r="Z324" s="4"/>
-      <c r="AA324" s="4"/>
-      <c r="AB324" s="4"/>
-      <c r="AC324" s="4"/>
-      <c r="AD324" s="4"/>
-      <c r="AE324" s="4"/>
-      <c r="AF324" s="4"/>
-      <c r="AG324" s="4"/>
-    </row>
-    <row r="373" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B373" s="4" t="s">
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6"/>
+      <c r="H181" s="6"/>
+      <c r="I181" s="6"/>
+      <c r="J181" s="6"/>
+      <c r="K181" s="6"/>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="6"/>
+      <c r="O181" s="6"/>
+      <c r="P181" s="6"/>
+      <c r="Q181" s="6"/>
+      <c r="R181" s="6"/>
+      <c r="S181" s="6"/>
+      <c r="T181" s="6"/>
+      <c r="U181" s="6"/>
+      <c r="V181" s="6"/>
+      <c r="W181" s="6"/>
+      <c r="X181" s="6"/>
+      <c r="Y181" s="6"/>
+      <c r="Z181" s="6"/>
+      <c r="AA181" s="6"/>
+      <c r="AB181" s="6"/>
+      <c r="AC181" s="6"/>
+      <c r="AD181" s="6"/>
+      <c r="AE181" s="6"/>
+      <c r="AF181" s="6"/>
+      <c r="AG181" s="6"/>
+    </row>
+    <row r="257" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B257" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C373" s="4"/>
-      <c r="D373" s="4"/>
-      <c r="E373" s="4"/>
-      <c r="F373" s="4"/>
-      <c r="G373" s="4"/>
-      <c r="H373" s="4"/>
-      <c r="I373" s="4"/>
-      <c r="J373" s="4"/>
-      <c r="K373" s="4"/>
-      <c r="L373" s="4"/>
-      <c r="M373" s="4"/>
-      <c r="N373" s="4"/>
-      <c r="O373" s="4"/>
-      <c r="P373" s="4"/>
-      <c r="Q373" s="4"/>
-      <c r="R373" s="4"/>
-      <c r="S373" s="4"/>
-      <c r="T373" s="4"/>
-      <c r="U373" s="4"/>
-      <c r="V373" s="4"/>
-      <c r="W373" s="4"/>
-      <c r="X373" s="4"/>
-      <c r="Y373" s="4"/>
-      <c r="Z373" s="4"/>
-      <c r="AA373" s="4"/>
-      <c r="AB373" s="4"/>
-      <c r="AC373" s="4"/>
-      <c r="AD373" s="4"/>
-      <c r="AE373" s="4"/>
-      <c r="AF373" s="4"/>
-      <c r="AG373" s="4"/>
-    </row>
-    <row r="430" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B430" s="4" t="s">
+      <c r="C257" s="4"/>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4"/>
+      <c r="G257" s="4"/>
+      <c r="H257" s="4"/>
+      <c r="I257" s="4"/>
+      <c r="J257" s="4"/>
+      <c r="K257" s="4"/>
+      <c r="L257" s="4"/>
+      <c r="M257" s="4"/>
+      <c r="N257" s="4"/>
+      <c r="O257" s="4"/>
+      <c r="P257" s="4"/>
+      <c r="Q257" s="4"/>
+      <c r="R257" s="4"/>
+      <c r="S257" s="4"/>
+      <c r="T257" s="4"/>
+      <c r="U257" s="4"/>
+      <c r="V257" s="4"/>
+      <c r="W257" s="4"/>
+      <c r="X257" s="4"/>
+      <c r="Y257" s="4"/>
+      <c r="Z257" s="4"/>
+      <c r="AA257" s="4"/>
+      <c r="AB257" s="4"/>
+      <c r="AC257" s="4"/>
+      <c r="AD257" s="4"/>
+      <c r="AE257" s="4"/>
+      <c r="AF257" s="4"/>
+      <c r="AG257" s="4"/>
+    </row>
+    <row r="331" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B331" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C430" s="4"/>
-      <c r="D430" s="4"/>
-      <c r="E430" s="4"/>
-      <c r="F430" s="4"/>
-      <c r="G430" s="4"/>
-      <c r="H430" s="4"/>
-      <c r="I430" s="4"/>
-      <c r="J430" s="4"/>
-      <c r="K430" s="4"/>
-      <c r="L430" s="4"/>
-      <c r="M430" s="4"/>
-      <c r="N430" s="4"/>
-      <c r="O430" s="4"/>
-      <c r="P430" s="4"/>
-      <c r="Q430" s="4"/>
-      <c r="R430" s="4"/>
-      <c r="S430" s="4"/>
-      <c r="T430" s="4"/>
-      <c r="U430" s="4"/>
-      <c r="V430" s="4"/>
-      <c r="W430" s="4"/>
-      <c r="X430" s="4"/>
-      <c r="Y430" s="4"/>
-      <c r="Z430" s="4"/>
-      <c r="AA430" s="4"/>
-      <c r="AB430" s="4"/>
-      <c r="AC430" s="4"/>
-      <c r="AD430" s="4"/>
-      <c r="AE430" s="4"/>
-      <c r="AF430" s="4"/>
-      <c r="AG430" s="4"/>
-    </row>
-    <row r="431" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B431" s="6" t="s">
+      <c r="C331" s="4"/>
+      <c r="D331" s="4"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+      <c r="G331" s="4"/>
+      <c r="H331" s="4"/>
+      <c r="I331" s="4"/>
+      <c r="J331" s="4"/>
+      <c r="K331" s="4"/>
+      <c r="L331" s="4"/>
+      <c r="M331" s="4"/>
+      <c r="N331" s="4"/>
+      <c r="O331" s="4"/>
+      <c r="P331" s="4"/>
+      <c r="Q331" s="4"/>
+      <c r="R331" s="4"/>
+      <c r="S331" s="4"/>
+      <c r="T331" s="4"/>
+      <c r="U331" s="4"/>
+      <c r="V331" s="4"/>
+      <c r="W331" s="4"/>
+      <c r="X331" s="4"/>
+      <c r="Y331" s="4"/>
+      <c r="Z331" s="4"/>
+      <c r="AA331" s="4"/>
+      <c r="AB331" s="4"/>
+      <c r="AC331" s="4"/>
+      <c r="AD331" s="4"/>
+      <c r="AE331" s="4"/>
+      <c r="AF331" s="4"/>
+      <c r="AG331" s="4"/>
+    </row>
+    <row r="380" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B380" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C431" s="6"/>
-      <c r="D431" s="6"/>
-      <c r="E431" s="6"/>
-      <c r="F431" s="6"/>
-      <c r="G431" s="6"/>
-      <c r="H431" s="6"/>
-      <c r="I431" s="6"/>
-      <c r="J431" s="6"/>
-      <c r="K431" s="6"/>
-      <c r="L431" s="6"/>
-      <c r="M431" s="6"/>
-      <c r="N431" s="6"/>
-      <c r="O431" s="6"/>
-      <c r="P431" s="6"/>
-      <c r="Q431" s="6"/>
-      <c r="R431" s="6"/>
-      <c r="S431" s="6"/>
-      <c r="T431" s="6"/>
-      <c r="U431" s="6"/>
-      <c r="V431" s="6"/>
-      <c r="W431" s="6"/>
-      <c r="X431" s="6"/>
-      <c r="Y431" s="6"/>
-      <c r="Z431" s="6"/>
-      <c r="AA431" s="6"/>
-      <c r="AB431" s="6"/>
-      <c r="AC431" s="6"/>
-      <c r="AD431" s="6"/>
-      <c r="AE431" s="6"/>
-      <c r="AF431" s="6"/>
-      <c r="AG431" s="6"/>
+      <c r="C380" s="4"/>
+      <c r="D380" s="4"/>
+      <c r="E380" s="4"/>
+      <c r="F380" s="4"/>
+      <c r="G380" s="4"/>
+      <c r="H380" s="4"/>
+      <c r="I380" s="4"/>
+      <c r="J380" s="4"/>
+      <c r="K380" s="4"/>
+      <c r="L380" s="4"/>
+      <c r="M380" s="4"/>
+      <c r="N380" s="4"/>
+      <c r="O380" s="4"/>
+      <c r="P380" s="4"/>
+      <c r="Q380" s="4"/>
+      <c r="R380" s="4"/>
+      <c r="S380" s="4"/>
+      <c r="T380" s="4"/>
+      <c r="U380" s="4"/>
+      <c r="V380" s="4"/>
+      <c r="W380" s="4"/>
+      <c r="X380" s="4"/>
+      <c r="Y380" s="4"/>
+      <c r="Z380" s="4"/>
+      <c r="AA380" s="4"/>
+      <c r="AB380" s="4"/>
+      <c r="AC380" s="4"/>
+      <c r="AD380" s="4"/>
+      <c r="AE380" s="4"/>
+      <c r="AF380" s="4"/>
+      <c r="AG380" s="4"/>
+    </row>
+    <row r="437" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B437" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C437" s="4"/>
+      <c r="D437" s="4"/>
+      <c r="E437" s="4"/>
+      <c r="F437" s="4"/>
+      <c r="G437" s="4"/>
+      <c r="H437" s="4"/>
+      <c r="I437" s="4"/>
+      <c r="J437" s="4"/>
+      <c r="K437" s="4"/>
+      <c r="L437" s="4"/>
+      <c r="M437" s="4"/>
+      <c r="N437" s="4"/>
+      <c r="O437" s="4"/>
+      <c r="P437" s="4"/>
+      <c r="Q437" s="4"/>
+      <c r="R437" s="4"/>
+      <c r="S437" s="4"/>
+      <c r="T437" s="4"/>
+      <c r="U437" s="4"/>
+      <c r="V437" s="4"/>
+      <c r="W437" s="4"/>
+      <c r="X437" s="4"/>
+      <c r="Y437" s="4"/>
+      <c r="Z437" s="4"/>
+      <c r="AA437" s="4"/>
+      <c r="AB437" s="4"/>
+      <c r="AC437" s="4"/>
+      <c r="AD437" s="4"/>
+      <c r="AE437" s="4"/>
+      <c r="AF437" s="4"/>
+      <c r="AG437" s="4"/>
+    </row>
+    <row r="438" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B438" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C438" s="6"/>
+      <c r="D438" s="6"/>
+      <c r="E438" s="6"/>
+      <c r="F438" s="6"/>
+      <c r="G438" s="6"/>
+      <c r="H438" s="6"/>
+      <c r="I438" s="6"/>
+      <c r="J438" s="6"/>
+      <c r="K438" s="6"/>
+      <c r="L438" s="6"/>
+      <c r="M438" s="6"/>
+      <c r="N438" s="6"/>
+      <c r="O438" s="6"/>
+      <c r="P438" s="6"/>
+      <c r="Q438" s="6"/>
+      <c r="R438" s="6"/>
+      <c r="S438" s="6"/>
+      <c r="T438" s="6"/>
+      <c r="U438" s="6"/>
+      <c r="V438" s="6"/>
+      <c r="W438" s="6"/>
+      <c r="X438" s="6"/>
+      <c r="Y438" s="6"/>
+      <c r="Z438" s="6"/>
+      <c r="AA438" s="6"/>
+      <c r="AB438" s="6"/>
+      <c r="AC438" s="6"/>
+      <c r="AD438" s="6"/>
+      <c r="AE438" s="6"/>
+      <c r="AF438" s="6"/>
+      <c r="AG438" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B56:AG56"/>
     <mergeCell ref="B112:AG112"/>
-    <mergeCell ref="B177:AG177"/>
-    <mergeCell ref="B178:AG178"/>
-    <mergeCell ref="B250:AG250"/>
-    <mergeCell ref="B324:AG324"/>
-    <mergeCell ref="B373:AG373"/>
-    <mergeCell ref="B430:AG430"/>
-    <mergeCell ref="B431:AG431"/>
+    <mergeCell ref="B180:AG180"/>
+    <mergeCell ref="B181:AG181"/>
+    <mergeCell ref="B257:AG257"/>
+    <mergeCell ref="B331:AG331"/>
+    <mergeCell ref="B380:AG380"/>
+    <mergeCell ref="B437:AG437"/>
+    <mergeCell ref="B438:AG438"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
@@ -3054,7 +3109,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3090,10 +3145,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -3104,22 +3159,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -3127,12 +3182,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -3145,33 +3200,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -3179,12 +3234,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -3197,33 +3252,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -3231,12 +3286,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -3249,33 +3304,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -3283,12 +3338,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -3301,33 +3356,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -3335,12 +3390,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -3353,33 +3408,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -3387,12 +3442,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -3405,33 +3460,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -3439,12 +3494,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -3457,33 +3512,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -3491,12 +3546,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -3509,33 +3564,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -3543,12 +3598,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -3561,33 +3616,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -3595,12 +3650,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -3613,33 +3668,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -3647,12 +3702,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -3665,33 +3720,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -3699,12 +3754,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -3717,33 +3772,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -3751,12 +3806,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -3769,33 +3824,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -3803,12 +3858,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -3821,33 +3876,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -3855,12 +3910,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -3873,33 +3928,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -3907,12 +3962,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -3925,33 +3980,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -3959,12 +4014,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -3977,33 +4032,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -4011,12 +4066,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -4029,33 +4084,33 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -4063,12 +4118,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -4078,7 +4133,7 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -4114,10 +4169,10 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -4128,22 +4183,22 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -4151,12 +4206,12 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z23" s="5"/>
       <c r="AA23" s="5"/>
       <c r="AB23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC23" s="5"/>
       <c r="AD23" s="5"/>
@@ -4169,33 +4224,33 @@
         <v>19</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -4203,12 +4258,12 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -4221,33 +4276,33 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -4255,12 +4310,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -4273,33 +4328,33 @@
         <v>21</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -4307,12 +4362,12 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -4325,33 +4380,33 @@
         <v>22</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -4359,12 +4414,12 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -4377,33 +4432,33 @@
         <v>23</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -4411,12 +4466,12 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -4429,33 +4484,33 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -4463,12 +4518,12 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -4478,7 +4533,7 @@
     </row>
     <row r="31" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -4514,10 +4569,10 @@
     </row>
     <row r="32" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -4528,22 +4583,22 @@
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -4551,12 +4606,12 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
       <c r="Y32" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
       <c r="AB32" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
@@ -4569,33 +4624,33 @@
         <v>25</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -4603,12 +4658,12 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -4621,33 +4676,33 @@
         <v>26</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -4655,12 +4710,12 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -4673,33 +4728,33 @@
         <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
@@ -4707,12 +4762,12 @@
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -4725,33 +4780,33 @@
         <v>28</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R36" s="3"/>
       <c r="S36" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
@@ -4759,12 +4814,12 @@
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -4777,33 +4832,33 @@
         <v>29</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P37" s="3"/>
       <c r="Q37" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R37" s="3"/>
       <c r="S37" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
@@ -4811,12 +4866,12 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -4826,7 +4881,7 @@
     </row>
     <row r="39" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -4862,10 +4917,10 @@
     </row>
     <row r="40" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -4876,22 +4931,22 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4899,12 +4954,12 @@
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
       <c r="Y40" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z40" s="5"/>
       <c r="AA40" s="5"/>
       <c r="AB40" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
@@ -4917,33 +4972,33 @@
         <v>30</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P41" s="3"/>
       <c r="Q41" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -4951,12 +5006,12 @@
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
       <c r="AB41" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -4964,38 +5019,38 @@
       <c r="AF41" s="3"/>
       <c r="AG41" s="3"/>
     </row>
-    <row r="42" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="42" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" s="7">
         <v>31</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R42" s="3"/>
       <c r="S42" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
@@ -5003,12 +5058,12 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
       <c r="AB42" s="3" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -5021,33 +5076,33 @@
         <v>32</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P43" s="3"/>
       <c r="Q43" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R43" s="3"/>
       <c r="S43" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
@@ -5055,12 +5110,12 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
       <c r="AB43" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -5073,33 +5128,33 @@
         <v>33</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R44" s="3"/>
       <c r="S44" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
@@ -5107,12 +5162,12 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
       <c r="AB44" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -5125,33 +5180,33 @@
         <v>34</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
@@ -5159,12 +5214,12 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
       <c r="AB45" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -5177,33 +5232,33 @@
         <v>35</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
@@ -5211,12 +5266,12 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -5229,33 +5284,33 @@
         <v>36</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P47" s="3"/>
       <c r="Q47" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
@@ -5263,12 +5318,12 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
       <c r="AB47" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -5281,33 +5336,33 @@
         <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R48" s="3"/>
       <c r="S48" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
@@ -5315,12 +5370,12 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
       <c r="AB48" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -5330,7 +5385,7 @@
     </row>
     <row r="50" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -5366,10 +5421,10 @@
     </row>
     <row r="51" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -5380,22 +5435,22 @@
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
       <c r="O51" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P51" s="5"/>
       <c r="Q51" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R51" s="5"/>
       <c r="S51" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -5403,12 +5458,12 @@
       <c r="W51" s="5"/>
       <c r="X51" s="5"/>
       <c r="Y51" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z51" s="5"/>
       <c r="AA51" s="5"/>
       <c r="AB51" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC51" s="5"/>
       <c r="AD51" s="5"/>
@@ -5421,33 +5476,33 @@
         <v>38</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
@@ -5455,12 +5510,12 @@
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
       <c r="AB52" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -5473,33 +5528,33 @@
         <v>39</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P53" s="3"/>
       <c r="Q53" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
@@ -5507,12 +5562,12 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
       <c r="AB53" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -5525,33 +5580,33 @@
         <v>40</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P54" s="3"/>
       <c r="Q54" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
@@ -5559,12 +5614,12 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
       <c r="AB54" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -5577,33 +5632,33 @@
         <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P55" s="3"/>
       <c r="Q55" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
@@ -5611,12 +5666,12 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -5629,33 +5684,33 @@
         <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R56" s="3"/>
       <c r="S56" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
@@ -5663,12 +5718,12 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -5678,7 +5733,7 @@
     </row>
     <row r="58" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
@@ -5714,10 +5769,10 @@
     </row>
     <row r="59" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -5728,22 +5783,22 @@
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R59" s="5"/>
       <c r="S59" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -5751,12 +5806,12 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
       <c r="Y59" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
       <c r="AB59" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC59" s="5"/>
       <c r="AD59" s="5"/>
@@ -5769,33 +5824,33 @@
         <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R60" s="3"/>
       <c r="S60" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
@@ -5803,12 +5858,12 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
       <c r="AB60" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -5818,7 +5873,7 @@
     </row>
     <row r="62" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -5854,10 +5909,10 @@
     </row>
     <row r="63" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B63" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -5868,22 +5923,22 @@
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
       <c r="O63" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P63" s="5"/>
       <c r="Q63" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R63" s="5"/>
       <c r="S63" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
@@ -5891,12 +5946,12 @@
       <c r="W63" s="5"/>
       <c r="X63" s="5"/>
       <c r="Y63" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z63" s="5"/>
       <c r="AA63" s="5"/>
       <c r="AB63" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC63" s="5"/>
       <c r="AD63" s="5"/>
@@ -5909,33 +5964,33 @@
         <v>44</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P64" s="3"/>
       <c r="Q64" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R64" s="3"/>
       <c r="S64" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
@@ -5943,12 +5998,12 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
       <c r="AB64" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -5958,7 +6013,7 @@
     </row>
     <row r="66" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -5994,10 +6049,10 @@
     </row>
     <row r="67" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -6008,22 +6063,22 @@
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
       <c r="O67" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P67" s="5"/>
       <c r="Q67" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R67" s="5"/>
       <c r="S67" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="5"/>
@@ -6031,12 +6086,12 @@
       <c r="W67" s="5"/>
       <c r="X67" s="5"/>
       <c r="Y67" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z67" s="5"/>
       <c r="AA67" s="5"/>
       <c r="AB67" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC67" s="5"/>
       <c r="AD67" s="5"/>
@@ -6049,33 +6104,33 @@
         <v>45</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R68" s="3"/>
       <c r="S68" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
@@ -6083,12 +6138,12 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
       <c r="AB68" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
@@ -6549,7 +6604,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6585,7 +6640,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -6621,10 +6676,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -6659,10 +6714,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -6697,10 +6752,10 @@
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -6735,10 +6790,10 @@
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -6773,10 +6828,10 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -6811,10 +6866,10 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -6849,7 +6904,7 @@
     </row>
     <row r="10" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -6885,13 +6940,13 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -6901,7 +6956,7 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -6910,7 +6965,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -6927,13 +6982,13 @@
     </row>
     <row r="12" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -6943,7 +6998,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -6952,7 +7007,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -6969,13 +7024,13 @@
     </row>
     <row r="13" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -6985,7 +7040,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -6994,7 +7049,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -7011,13 +7066,13 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -7027,7 +7082,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -7036,7 +7091,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -7053,13 +7108,13 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -7069,7 +7124,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -7078,7 +7133,7 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -7095,13 +7150,13 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -7111,7 +7166,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -7120,7 +7175,7 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -7137,13 +7192,13 @@
     </row>
     <row r="17" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -7153,7 +7208,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -7162,7 +7217,7 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -7179,13 +7234,13 @@
     </row>
     <row r="18" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -7195,7 +7250,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -7204,7 +7259,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -7221,13 +7276,13 @@
     </row>
     <row r="19" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -7237,7 +7292,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -7246,7 +7301,7 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -7263,13 +7318,13 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -7279,7 +7334,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -7288,7 +7343,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -7305,13 +7360,13 @@
     </row>
     <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -7321,7 +7376,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -7330,7 +7385,7 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -7347,7 +7402,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -7383,7 +7438,7 @@
     </row>
     <row r="24" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -7419,10 +7474,10 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -7457,10 +7512,10 @@
     </row>
     <row r="26" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -7495,10 +7550,10 @@
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -7533,7 +7588,7 @@
     </row>
     <row r="29" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -7569,14 +7624,14 @@
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -7607,14 +7662,14 @@
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -7645,14 +7700,14 @@
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -7683,14 +7738,14 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -7721,14 +7776,14 @@
     </row>
     <row r="34" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -7759,14 +7814,14 @@
     </row>
     <row r="35" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -7797,14 +7852,14 @@
     </row>
     <row r="36" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -7835,14 +7890,14 @@
     </row>
     <row r="37" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -7873,7 +7928,7 @@
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -7909,7 +7964,7 @@
     </row>
     <row r="40" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -7945,7 +8000,7 @@
     </row>
     <row r="41" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -7959,11 +8014,11 @@
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="O41" s="5"/>
       <c r="P41" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
@@ -7985,7 +8040,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -8003,7 +8058,7 @@
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -8025,7 +8080,7 @@
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -8043,7 +8098,7 @@
       </c>
       <c r="O43" s="7"/>
       <c r="P43" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -8065,7 +8120,7 @@
     </row>
     <row r="44" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -8083,7 +8138,7 @@
       </c>
       <c r="O44" s="7"/>
       <c r="P44" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
@@ -8105,7 +8160,7 @@
     </row>
     <row r="45" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -8123,7 +8178,7 @@
       </c>
       <c r="O45" s="7"/>
       <c r="P45" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -8145,7 +8200,7 @@
     </row>
     <row r="46" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -8163,7 +8218,7 @@
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
@@ -8185,7 +8240,7 @@
     </row>
     <row r="47" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -8203,7 +8258,7 @@
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
@@ -8225,7 +8280,7 @@
     </row>
     <row r="48" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -8239,11 +8294,11 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
@@ -8265,7 +8320,7 @@
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -8283,7 +8338,7 @@
       </c>
       <c r="O49" s="7"/>
       <c r="P49" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
@@ -8305,7 +8360,7 @@
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -8323,7 +8378,7 @@
       </c>
       <c r="O50" s="7"/>
       <c r="P50" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
@@ -8345,7 +8400,7 @@
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -8363,7 +8418,7 @@
       </c>
       <c r="O51" s="7"/>
       <c r="P51" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
@@ -8385,7 +8440,7 @@
     </row>
     <row r="52" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -8403,7 +8458,7 @@
       </c>
       <c r="O52" s="7"/>
       <c r="P52" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
@@ -8425,7 +8480,7 @@
     </row>
     <row r="53" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -8439,11 +8494,11 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -8465,7 +8520,7 @@
     </row>
     <row r="54" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -8483,7 +8538,7 @@
       </c>
       <c r="O54" s="7"/>
       <c r="P54" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -8505,7 +8560,7 @@
     </row>
     <row r="55" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -8523,7 +8578,7 @@
       </c>
       <c r="O55" s="7"/>
       <c r="P55" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -8545,7 +8600,7 @@
     </row>
     <row r="56" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -8563,7 +8618,7 @@
       </c>
       <c r="O56" s="7"/>
       <c r="P56" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
@@ -8585,7 +8640,7 @@
     </row>
     <row r="58" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
